--- a/外來文件清單.xlsx
+++ b/外來文件清單.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\day75\OneDrive\文件\MEGAsync\Leon\久方\暫存區\處理案件\久方軟體\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\day75\OneDrive\文件\MEGAsync\Leon\久方\暫存區\處理案件\久方軟體\med-recall-monitor-for-win-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097363E8-82C3-4782-AE29-CC9348A648F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43491559-806F-4020-87E9-BFB907FBE38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F13F4BC-1310-4627-97C8-78E6FE7D69AD}"/>
   </bookViews>
